--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -17,13 +17,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -63,12 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,3759 +440,3769 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>company_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>company_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>EV_EBITDA</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>fcf_yield_pct</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>5yr_median_PE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>pe_vs_sector_median_pct</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Abbott India Ltd</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>75.58</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>12.63</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.05188004157485571</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>62.63</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>60.27992789735976</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Caution</t>
+          <t>⚠️ NOTE: P/E, P/B, EV/EBITDA, and market cap figures are SIMULATED data, not real market prices — for demonstration purposes only.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>company_id</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>EV_EBITDA</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>fcf_yield_pct</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>5yr_median_PE</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>pe_vs_sector_median_pct</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Abbott India Ltd</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.05188004157485571</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>60.27992789735976</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>ADANIENSOL</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Adani Energy Solutions Ltd</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>14.83</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>0.3141880794689826</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>30.24602026049203</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Adani Enterprises Ltd</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>58.87</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>10.41</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>33.01</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>-4.499064189327432</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>58.87</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>24.84360089067967</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ADANIGREEN</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Adani Green Energy Ltd</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>45.26</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>6.24</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>21.78</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>-2.61443014217979</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>37.61</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>0.7681175553823971</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Adani Ports &amp; Special Economic Zone Ltd
 </t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>48.9</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>2.31</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>31.76</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>1.221140364223394</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>48.9</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>3.700561976460603</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>ADANIPOWER</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Adani Power Ltd</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>44.57</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>9.91</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>24.76</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>1.286343944292292</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>52.23</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.768117555382386</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>AMBUJACEM</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Ambuja Cements Ltd</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>55.62</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>27.67</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>-0.2571384120430241</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>55.62</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Apollo Hospitals
 Chain of Indian private hospitals</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>47.72</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <v>7.68</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>16.74</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>0.0200984200212211</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>28.39</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>1.402464938376524</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Asian Paints
 Indian Multi-National Paint and Coating Manufacturing Company</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>73.37</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>23.94</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G12" s="3" t="n">
         <v>0.167205430839917</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H12" s="3" t="n">
         <v>49.2</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I12" s="3" t="n">
         <v>31.91298094210717</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>ATGL</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Adani Total Gas Ltd</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>56.96</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <v>5.76</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>28.93</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H13" s="3" t="n">
         <v>35.59</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I13" s="3" t="n">
         <v>26.8173216074808</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Axis Bank Ltd</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>38.14</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <v>4.66</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F14" s="3" t="n">
         <v>16.87</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G14" s="3" t="n">
         <v>-1.534037435719632</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H14" s="3" t="n">
         <v>56.88</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I14" s="3" t="n">
         <v>11.39018691588785</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Bajaj Auto Ltd</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>29.91</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <v>9.83</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F15" s="3" t="n">
         <v>20.14</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>0.992020247858232</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H15" s="3" t="n">
         <v>49.72</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I15" s="3" t="n">
         <v>-21.29982896987239</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Bajaj Finserv Ltd</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>15.07</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E16" s="3" t="n">
         <v>6.08</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F16" s="3" t="n">
         <v>39.72</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G16" s="3" t="n">
         <v>-4.180016339930263</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H16" s="3" t="n">
         <v>51.06</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <v>-55.98714953271029</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>BAJAJHLDNG</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Bajaj Holdings &amp; Investment Ltd</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>37.73</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E17" s="3" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F17" s="3" t="n">
         <v>27.47</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G17" s="3" t="n">
         <v>0.06702962960133939</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H17" s="3" t="n">
         <v>37.73</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I17" s="3" t="n">
         <v>10.19275700934579</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Bajaj Finance Ltd</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>69.2</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E18" s="3" t="n">
         <v>4.11</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F18" s="3" t="n">
         <v>15.96</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>-3.231792280571145</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H18" s="3" t="n">
         <v>46.9</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I18" s="3" t="n">
         <v>102.1028037383178</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>BANKBARODA</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Bank of Baroda</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D19" s="3" t="n">
         <v>16.89</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E19" s="3" t="n">
         <v>4.15</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F19" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G19" s="3" t="n">
         <v>-1.279081332956056</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H19" s="3" t="n">
         <v>67.23999999999999</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I19" s="3" t="n">
         <v>-50.67172897196262</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Bharat Electronics Ltd</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D20" s="3" t="n">
         <v>17.89</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E20" s="3" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F20" s="3" t="n">
         <v>23.14</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <v>-0.09337302073000636</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H20" s="3" t="n">
         <v>52.67</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I20" s="3" t="n">
         <v>-62.06128724419469</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Bharti Airtel Ltd</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D21" s="3" t="n">
         <v>63.78</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E21" s="3" t="n">
         <v>6.28</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F21" s="3" t="n">
         <v>39.71</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G21" s="3" t="n">
         <v>7.345106122639473</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H21" s="3" t="n">
         <v>63.78</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I21" s="3" t="n">
         <v>31.967721911856</v>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Bharat Heavy Electricals Limited
 </t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D22" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E22" s="3" t="n">
         <v>11.43</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F22" s="3" t="n">
         <v>21.59</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G22" s="3" t="n">
         <v>-0.4410671269170658</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H22" s="3" t="n">
         <v>31.13</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I22" s="3" t="n">
         <v>-36.80415650514261</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>BOSCHLTD</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Bosch Ltd</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D23" s="3" t="n">
         <v>58.43</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E23" s="3" t="n">
         <v>6.47</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F23" s="3" t="n">
         <v>16.07</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G23" s="3" t="n">
         <v>0.05908701218425355</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H23" s="3" t="n">
         <v>31.28</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I23" s="3" t="n">
         <v>53.74292856203131</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>BPCL</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Bharat Petroleum Corporation Ltd</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D24" s="3" t="n">
         <v>68.15000000000001</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E24" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F24" s="3" t="n">
         <v>26.59</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G24" s="3" t="n">
         <v>5.422883218663305</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H24" s="3" t="n">
         <v>35.8</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I24" s="3" t="n">
         <v>51.73104753423134</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>BRITANNIA</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Britannia Industries Ltd</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D25" s="3" t="n">
         <v>63.91</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E25" s="3" t="n">
         <v>4.26</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F25" s="3" t="n">
         <v>33.95</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G25" s="3" t="n">
         <v>0.9391963078561093</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H25" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I25" s="3" t="n">
         <v>25.43670264965652</v>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>CANBK</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Canara Bank</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D26" s="3" t="n">
         <v>36.74</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E26" s="3" t="n">
         <v>12.61</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F26" s="3" t="n">
         <v>25.23</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G26" s="3" t="n">
         <v>2.678399409785198</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H26" s="3" t="n">
         <v>36.74</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I26" s="3" t="n">
         <v>7.301401869158886</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>CHOLAFIN</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Cholamandalam Investment &amp; Finance Company Ltd</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D27" s="3" t="n">
         <v>16.79</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E27" s="3" t="n">
         <v>10.36</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F27" s="3" t="n">
         <v>13.52</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G27" s="3" t="n">
         <v>-3.965092371280805</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H27" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I27" s="3" t="n">
         <v>-50.96378504672898</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Cipla Ltd
 </t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D28" s="3" t="n">
         <v>59.75</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E28" s="3" t="n">
         <v>5.93</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F28" s="3" t="n">
         <v>33.7</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G28" s="3" t="n">
         <v>0.2619353681300373</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H28" s="3" t="n">
         <v>41.07</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I28" s="3" t="n">
         <v>26.96557586060349</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Coal India Ltd</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D29" s="3" t="n">
         <v>34.27</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E29" s="3" t="n">
         <v>14.75</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F29" s="3" t="n">
         <v>25.15</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G29" s="3" t="n">
         <v>2.999175111211977</v>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H29" s="3" t="n">
         <v>32.17</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="I29" s="3" t="n">
         <v>-38.38547285149227</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>DABUR</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Dabur India Ltd</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D30" s="3" t="n">
         <v>50.95</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E30" s="3" t="n">
         <v>13.59</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F30" s="3" t="n">
         <v>12.02</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G30" s="3" t="n">
         <v>1.843535171537232</v>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H30" s="3" t="n">
         <v>50.95</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>DIVISLAB</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Divis Laboratories Ltd</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D31" s="3" t="n">
         <v>69.95</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E31" s="3" t="n">
         <v>12.34</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F31" s="3" t="n">
         <v>31.81</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G31" s="3" t="n">
         <v>0.0614230582049048</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H31" s="3" t="n">
         <v>30.35</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="I31" s="3" t="n">
         <v>48.64003399915002</v>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>DLF Ltd</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D32" s="3" t="n">
         <v>46.26</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E32" s="3" t="n">
         <v>14.32</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F32" s="3" t="n">
         <v>10.41</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G32" s="3" t="n">
         <v>0.07309772065891328</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H32" s="3" t="n">
         <v>46.26</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I32" s="3" t="n">
         <v>-5.793707361775802</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>DMART</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Avenue Supermarts Ltd</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D33" s="3" t="n">
         <v>72.53</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E33" s="3" t="n">
         <v>11.71</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F33" s="3" t="n">
         <v>36.84</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G33" s="3" t="n">
         <v>0.00910553222430331</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H33" s="3" t="n">
         <v>37.82</v>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="I33" s="3" t="n">
         <v>90.84331009077754</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Dr Reddys Laboratories Ltd</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D34" s="3" t="n">
         <v>11.73</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E34" s="3" t="n">
         <v>10.19</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F34" s="3" t="n">
         <v>14.56</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G34" s="3" t="n">
         <v>0.02084525007272494</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H34" s="3" t="n">
         <v>13.03</v>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="I34" s="3" t="n">
         <v>-75.07437314067148</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Eicher Motors Ltd</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D35" s="3" t="n">
         <v>15.62</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E35" s="3" t="n">
         <v>13.61</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F35" s="3" t="n">
         <v>19.29</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G35" s="3" t="n">
         <v>0.4001945575069012</v>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H35" s="3" t="n">
         <v>18.91</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="I35" s="3" t="n">
         <v>-58.90014471780029</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>GAIL</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>GAIL (India) Ltd</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D36" s="3" t="n">
         <v>25.84</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E36" s="3" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F36" s="3" t="n">
         <v>33.07</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G36" s="3" t="n">
         <v>0.2846199035338283</v>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H36" s="3" t="n">
         <v>30.66</v>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="I36" s="3" t="n">
         <v>-42.46910831570745</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>GODREJCP</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Godrej Consumer Products Ltd</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D37" s="3" t="n">
         <v>33.59</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E37" s="3" t="n">
         <v>8.07</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F37" s="3" t="n">
         <v>23.55</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G37" s="3" t="n">
         <v>-0.1028018435345398</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H37" s="3" t="n">
         <v>40.79</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="I37" s="3" t="n">
         <v>-34.07262021589793</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Grasim Industries Ltd</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D38" s="3" t="n">
         <v>79.34999999999999</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E38" s="3" t="n">
         <v>5.68</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F38" s="3" t="n">
         <v>15.23</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G38" s="3" t="n">
         <v>-7.063967310949983</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H38" s="3" t="n">
         <v>38.27</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I38" s="3" t="n">
         <v>68.27483829922593</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>HAL</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Hindustan Aeronautics Ltd</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D39" s="3" t="n">
         <v>71.89</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E39" s="3" t="n">
         <v>3.65</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F39" s="3" t="n">
         <v>8.76</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G39" s="3" t="n">
         <v>0.06861811283803056</v>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H39" s="3" t="n">
         <v>51.22</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="I39" s="3" t="n">
         <v>52.45467076662072</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>HAVELLS</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Havells India Ltd</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D40" s="3" t="n">
         <v>45.41</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E40" s="3" t="n">
         <v>14.08</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F40" s="3" t="n">
         <v>30.73</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G40" s="3" t="n">
         <v>0.01328569587780193</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H40" s="3" t="n">
         <v>45.41</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I40" s="3" t="n">
         <v>-3.700561976460615</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>HCL Technologies Ltd</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D41" s="3" t="n">
         <v>63.63</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E41" s="3" t="n">
         <v>5.44</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F41" s="3" t="n">
         <v>31.21</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G41" s="3" t="n">
         <v>3.839131751270119</v>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H41" s="3" t="n">
         <v>63.63</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="I41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>HDFC Bank Ltd</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D42" s="3" t="n">
         <v>49.42</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E42" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F42" s="3" t="n">
         <v>22.54</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G42" s="3" t="n">
         <v>4.412519521183551</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H42" s="3" t="n">
         <v>30.19</v>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="I42" s="3" t="n">
         <v>44.33411214953271</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>HDFC Life Insurance Company Ltd</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D43" s="3" t="n">
         <v>50.59</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E43" s="3" t="n">
         <v>11.28</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F43" s="3" t="n">
         <v>31.63</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G43" s="3" t="n">
         <v>-6.151706657367163</v>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="H43" s="3" t="n">
         <v>50.59</v>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="I43" s="3" t="n">
         <v>47.75116822429906</v>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>HEROMOTOCO</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Hero MotoCorp Ltd
 </t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D44" s="3" t="n">
         <v>53.86</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E44" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F44" s="3" t="n">
         <v>28.27</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G44" s="3" t="n">
         <v>0.1942386275072222</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H44" s="3" t="n">
         <v>56.18</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I44" s="3" t="n">
         <v>41.71819497434548</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Hindalco Industries Ltd</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D45" s="3" t="n">
         <v>56.45</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E45" s="3" t="n">
         <v>9.32</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F45" s="3" t="n">
         <v>27.63</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G45" s="3" t="n">
         <v>1.355289512628809</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H45" s="3" t="n">
         <v>56.45</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I45" s="3" t="n">
         <v>1.492268967997123</v>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Hindustan Unilever Ltd
 </t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D46" s="3" t="n">
         <v>34.51</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E46" s="3" t="n">
         <v>11.88</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F46" s="3" t="n">
         <v>7.52</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G46" s="3" t="n">
         <v>1.848273624075064</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H46" s="3" t="n">
         <v>22.92</v>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="I46" s="3" t="n">
         <v>-32.26692836113838</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>ICICI Bank Ltd</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D47" s="3" t="n">
         <v>25.76</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E47" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F47" s="3" t="n">
         <v>38.28</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G47" s="3" t="n">
         <v>0.9510909711578005</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H47" s="3" t="n">
         <v>25.76</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="I47" s="3" t="n">
         <v>-24.76635514018691</v>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>ICICI Lombard General Insurance Company Ltd</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D48" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E48" s="3" t="n">
         <v>7.86</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F48" s="3" t="n">
         <v>36.96</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G48" s="3" t="n">
         <v>0.03821387979852416</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H48" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I48" s="3" t="n">
         <v>43.10747663551402</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>ICICIPRULI</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>ICICI Prudential Life Insurance Company Ltd</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>20.83</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E49" s="3" t="n">
         <v>12.38</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F49" s="3" t="n">
         <v>22.57</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G49" s="3" t="n">
         <v>0.006574879059013327</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H49" s="3" t="n">
         <v>36.03</v>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="I49" s="3" t="n">
         <v>-39.16471962616824</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Interglobe Aviation Ltd</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D50" s="3" t="n">
         <v>76.23</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E50" s="3" t="n">
         <v>7.87</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F50" s="3" t="n">
         <v>24.64</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G50" s="3" t="n">
         <v>0.9056027172386589</v>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H50" s="3" t="n">
         <v>51.42</v>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I50" s="3" t="n">
         <v>100.5788712011578</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>IndusInd Bank Ltd</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D51" s="3" t="n">
         <v>8.99</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E51" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F51" s="3" t="n">
         <v>28.79</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G51" s="3" t="n">
         <v>-0.9664534641259643</v>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H51" s="3" t="n">
         <v>51.73</v>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="I51" s="3" t="n">
         <v>-73.74415887850468</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Infosys Ltd</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D52" s="3" t="n">
         <v>35.99</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E52" s="3" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F52" s="3" t="n">
         <v>36.7</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G52" s="3" t="n">
         <v>1.808627454139422</v>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H52" s="3" t="n">
         <v>35.99</v>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I52" s="3" t="n">
         <v>-43.43862957724344</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Indian Oil Corporation
 </t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D53" s="3" t="n">
         <v>28.61</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E53" s="3" t="n">
         <v>4.24</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F53" s="3" t="n">
         <v>33.71</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G53" s="3" t="n">
         <v>2.794810104975634</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H53" s="3" t="n">
         <v>50.51</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I53" s="3" t="n">
         <v>-36.30190359568073</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>IRCTC</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D54" s="3" t="n">
         <v>60.44</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E54" s="3" t="n">
         <v>5.74</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F54" s="3" t="n">
         <v>32.47</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G54" s="3" t="n">
         <v>0.05299874823631171</v>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="H54" s="3" t="n">
         <v>36.42</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I54" s="3" t="n">
         <v>59.03170635442703</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>IRFC</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Indian Railway Finance Corporation Ltd</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D55" s="3" t="n">
         <v>9.81</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E55" s="3" t="n">
         <v>3.91</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F55" s="3" t="n">
         <v>16.66</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G55" s="3" t="n">
         <v>0.3019460457018293</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H55" s="3" t="n">
         <v>37.81</v>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="I55" s="3" t="n">
         <v>-71.34929906542055</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ITC Ltd
 </t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D56" s="3" t="n">
         <v>47.85</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E56" s="3" t="n">
         <v>3.24</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F56" s="3" t="n">
         <v>17.19</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G56" s="3" t="n">
         <v>5.641008076014133</v>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H56" s="3" t="n">
         <v>55.53</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I56" s="3" t="n">
         <v>-6.08439646712463</v>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>JINDALSTEL</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Jindal Steel &amp; Power Ltd</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D57" s="3" t="n">
         <v>77.64</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E57" s="3" t="n">
         <v>5.73</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F57" s="3" t="n">
         <v>20.22</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G57" s="3" t="n">
         <v>-0.5890244225007633</v>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="H57" s="3" t="n">
         <v>47.36</v>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="I57" s="3" t="n">
         <v>39.59007551240561</v>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Jio Financial Services Ltd</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D58" s="3" t="n">
         <v>34.24</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E58" s="3" t="n">
         <v>9.91</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F58" s="3" t="n">
         <v>26.41</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G58" s="3" t="n">
         <v>0.05443098966974722</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H58" s="3" t="n">
         <v>65.98</v>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="I58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>JSWENERGY</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>JSW Energy Ltd</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D59" s="3" t="n">
         <v>24.79</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E59" s="3" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F59" s="3" t="n">
         <v>35.95</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G59" s="3" t="n">
         <v>-1.77053361249378</v>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="H59" s="3" t="n">
         <v>36.57</v>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="I59" s="3" t="n">
         <v>-44.80685739730602</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>JSW Steel Ltd</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D60" s="3" t="n">
         <v>69.27</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E60" s="3" t="n">
         <v>4.37</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="F60" s="3" t="n">
         <v>35.49</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G60" s="3" t="n">
         <v>-0.09143985264473488</v>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H60" s="3" t="n">
         <v>36.76</v>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="I60" s="3" t="n">
         <v>24.54153182308523</v>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Kotak Mahindra Bank Ltd
 </t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D61" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E61" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F61" s="3" t="n">
         <v>15.52</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G61" s="3" t="n">
         <v>1.572670875827523</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H61" s="3" t="n">
         <v>43.71</v>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="I61" s="3" t="n">
         <v>-3.913551401869164</v>
       </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>LICI</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Life Insurance Corporation of India</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D62" s="3" t="n">
         <v>30.67</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E62" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="F62" s="3" t="n">
         <v>12.21</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G62" s="3" t="n">
         <v>0.4646382763782856</v>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="H62" s="3" t="n">
         <v>30.67</v>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="I62" s="3" t="n">
         <v>-10.42640186915887</v>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>LODHA</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>Macrotech Developers Ltd</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D63" s="3" t="n">
         <v>51.95</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E63" s="3" t="n">
         <v>7.65</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F63" s="3" t="n">
         <v>34.33</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G63" s="3" t="n">
         <v>-0.03595279056427525</v>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="H63" s="3" t="n">
         <v>51.95</v>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="I63" s="3" t="n">
         <v>5.793707361775779</v>
       </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Larsen &amp; Toubro Ltd</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D64" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E64" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F64" s="3" t="n">
         <v>16.63</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G64" s="3" t="n">
         <v>1.817983767525715</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H64" s="3" t="n">
         <v>18.77</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I64" s="3" t="n">
         <v>-34.68349061605343</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>LTIM</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>LTIMindtree Ltd</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D65" s="3" t="n">
         <v>64.52</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E65" s="3" t="n">
         <v>2.38</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F65" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G65" s="3" t="n">
         <v>0.1300622866212008</v>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="H65" s="3" t="n">
         <v>61.37</v>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="I65" s="3" t="n">
         <v>1.398711299701394</v>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mahindra &amp; Mahindra Ltd
 </t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D66" s="3" t="n">
         <v>14.22</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E66" s="3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F66" s="3" t="n">
         <v>29.08</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G66" s="3" t="n">
         <v>-0.2694648852484086</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H66" s="3" t="n">
         <v>34.84</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I66" s="3" t="n">
         <v>-62.58387054334956</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Maruti Suzuki India Ltd</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D67" s="3" t="n">
         <v>20.78</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E67" s="3" t="n">
         <v>8.26</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F67" s="3" t="n">
         <v>29.97</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G67" s="3" t="n">
         <v>0.3282212496887102</v>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="H67" s="3" t="n">
         <v>20.78</v>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="I67" s="3" t="n">
         <v>-45.3229838179187</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>MOTHERSON</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Samvardhana Motherson International Ltd</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D68" s="3" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E68" s="3" t="n">
         <v>2.38</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F68" s="3" t="n">
         <v>33.39</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G68" s="3" t="n">
         <v>0.6329063689949501</v>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H68" s="3" t="n">
         <v>30.92</v>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="I68" s="3" t="n">
         <v>-74.89803973161426</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>NAUKRI</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Info Edge (India) Ltd</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D69" s="3" t="n">
         <v>32.88</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E69" s="3" t="n">
         <v>8.33</v>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F69" s="3" t="n">
         <v>11.87</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G69" s="3" t="n">
         <v>-0.02660402589146366</v>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="H69" s="3" t="n">
         <v>36.89</v>
       </c>
-      <c r="I67" s="2" t="n">
+      <c r="I69" s="3" t="n">
         <v>-31.96772191185599</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Nestle India Ltd</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D70" s="3" t="n">
         <v>54.96</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E70" s="3" t="n">
         <v>14.34</v>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F70" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G70" s="3" t="n">
         <v>0.175112852872738</v>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H70" s="3" t="n">
         <v>46.21</v>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="I70" s="3" t="n">
         <v>7.870461236506365</v>
       </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>NHPC</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">NHPC Ltd
 </t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D71" s="3" t="n">
         <v>71.17</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E71" s="3" t="n">
         <v>13.74</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="F71" s="3" t="n">
         <v>18.26</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G71" s="3" t="n">
         <v>0.05573417784977254</v>
       </c>
-      <c r="H69" s="2" t="n">
+      <c r="H71" s="3" t="n">
         <v>59.63</v>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="I71" s="3" t="n">
         <v>58.4548591784482</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>NTPC Ltd</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="D72" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E72" s="3" t="n">
         <v>5.24</v>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="F72" s="3" t="n">
         <v>37.12</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G72" s="3" t="n">
         <v>0.9521678733206076</v>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="H72" s="3" t="n">
         <v>54.44</v>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="I72" s="3" t="n">
         <v>-31.42602693977513</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>Oil &amp; Natural Gas Corpn Ltd</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D73" s="3" t="n">
         <v>18.15</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E73" s="3" t="n">
         <v>10.36</v>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="F73" s="3" t="n">
         <v>11.72</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G73" s="3" t="n">
         <v>10.78154540867274</v>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H73" s="3" t="n">
         <v>43.8</v>
       </c>
-      <c r="I71" s="2" t="n">
+      <c r="I73" s="3" t="n">
         <v>-59.59033730379606</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>PFC</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>Power Finance Corporation Ltd</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D74" s="3" t="n">
         <v>35.6</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E74" s="3" t="n">
         <v>6.59</v>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="F74" s="3" t="n">
         <v>15.67</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G74" s="3" t="n">
         <v>-5.031547988302576</v>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H74" s="3" t="n">
         <v>35.6</v>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="I74" s="3" t="n">
         <v>3.971962616822422</v>
       </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>PIDILITIND</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>Pidilite Industries Ltd</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D75" s="3" t="n">
         <v>36.12</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E75" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="F75" s="3" t="n">
         <v>5.36</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G75" s="3" t="n">
         <v>0.588510137595519</v>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="H75" s="3" t="n">
         <v>38.11</v>
       </c>
-      <c r="I73" s="2" t="n">
+      <c r="I75" s="3" t="n">
         <v>-35.05933117583603</v>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Punjab National Bank</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D76" s="3" t="n">
         <v>19.29</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E76" s="3" t="n">
         <v>10.91</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F76" s="3" t="n">
         <v>23.64</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G76" s="3" t="n">
         <v>-1.612606778720886</v>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="H76" s="3" t="n">
         <v>20.42</v>
       </c>
-      <c r="I74" s="2" t="n">
+      <c r="I76" s="3" t="n">
         <v>-43.6623831775701</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>Power Grid Corporation of India Ltd</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D77" s="3" t="n">
         <v>64.39</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E77" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="F77" s="3" t="n">
         <v>23.07</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G77" s="3" t="n">
         <v>6.488733930345523</v>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="H77" s="3" t="n">
         <v>37.33</v>
       </c>
-      <c r="I75" s="2" t="n">
+      <c r="I77" s="3" t="n">
         <v>43.35967939441168</v>
       </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>RECLTD</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>REC Ltd</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D78" s="3" t="n">
         <v>31.49</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E78" s="3" t="n">
         <v>4.59</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F78" s="3" t="n">
         <v>23.95</v>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G78" s="3" t="n">
         <v>-20.40097504287343</v>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="H78" s="3" t="n">
         <v>31.49</v>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="I78" s="3" t="n">
         <v>-8.03154205607478</v>
       </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Reliance Industries Ltd
 </t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D79" s="3" t="n">
         <v>58.34</v>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E79" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F79" s="3" t="n">
         <v>24.96</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G79" s="3" t="n">
         <v>10.45314512446346</v>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="H79" s="3" t="n">
         <v>58.34</v>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="I79" s="3" t="n">
         <v>29.88979182901037</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>SBI Life Insurance Company Ltd</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D80" s="3" t="n">
         <v>69.98</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E80" s="3" t="n">
         <v>9.48</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="F80" s="3" t="n">
         <v>31.04</v>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G80" s="3" t="n">
         <v>-0.2368813254240325</v>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H80" s="3" t="n">
         <v>60.68</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I80" s="3" t="n">
         <v>104.3808411214953</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>State Bank of India</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D81" s="3" t="n">
         <v>54.93</v>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E81" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="F81" s="3" t="n">
         <v>21.53</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G81" s="3" t="n">
         <v>0.7563625783740417</v>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H81" s="3" t="n">
         <v>54.93</v>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="I81" s="3" t="n">
         <v>60.42640186915887</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="J81" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>SHREECEM</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>Shree Cement Ltd</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="D82" s="3" t="n">
         <v>25.87</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E82" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="F82" s="3" t="n">
         <v>26.58</v>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="G82" s="3" t="n">
         <v>0.06115348347250073</v>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="H82" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="I82" s="3" t="n">
         <v>-53.48795397339086</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Shriram Finance Ltd
 </t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="D83" s="3" t="n">
         <v>68.53</v>
       </c>
-      <c r="E81" s="2" t="n">
+      <c r="E83" s="3" t="n">
         <v>7.91</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F83" s="3" t="n">
         <v>28.82</v>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G83" s="3" t="n">
         <v>-3.608906905151208</v>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="H83" s="3" t="n">
         <v>37.85</v>
       </c>
-      <c r="I81" s="2" t="n">
+      <c r="I83" s="3" t="n">
         <v>100.1460280373831</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
+      <c r="J83" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>SIEMENS</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>Siemens Ltd</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D84" s="3" t="n">
         <v>33.32</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E84" s="3" t="n">
         <v>9.25</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F84" s="3" t="n">
         <v>30.88</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G84" s="3" t="n">
         <v>0.09804152402695152</v>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H84" s="3" t="n">
         <v>41.13</v>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="I84" s="3" t="n">
         <v>-29.33941257554873</v>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>Sun Pharmaceuticals Industries Ltd</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="D85" s="3" t="n">
         <v>37.9</v>
       </c>
-      <c r="E83" s="2" t="n">
+      <c r="E85" s="3" t="n">
         <v>6.71</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="F85" s="3" t="n">
         <v>21.41</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="G85" s="3" t="n">
         <v>0.8489189373413096</v>
       </c>
-      <c r="H83" s="2" t="n">
+      <c r="H85" s="3" t="n">
         <v>24.58</v>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="I85" s="3" t="n">
         <v>-19.46451338716533</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>Tata Consumer Products Ltd</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="D86" s="3" t="n">
         <v>54.79</v>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="E86" s="3" t="n">
         <v>7.14</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="F86" s="3" t="n">
         <v>24.84</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="G86" s="3" t="n">
         <v>0.007417056977403794</v>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H86" s="3" t="n">
         <v>54.79</v>
       </c>
-      <c r="I84" s="2" t="n">
+      <c r="I86" s="3" t="n">
         <v>7.536800785083408</v>
       </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>TATAMOTORS</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>Tata Motors Ltd</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D87" s="3" t="n">
         <v>67.06999999999999</v>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E87" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="F87" s="3" t="n">
         <v>15.35</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="G87" s="3" t="n">
         <v>3.000651602734764</v>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="H87" s="3" t="n">
         <v>34.17</v>
       </c>
-      <c r="I85" s="2" t="n">
+      <c r="I87" s="3" t="n">
         <v>76.47677937113535</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
+      <c r="J87" s="4" t="inlineStr">
         <is>
           <t>Caution</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>TATAPOWER</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tata Power Company Ltd
 </t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D88" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="E88" s="3" t="n">
         <v>3.48</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="F88" s="3" t="n">
         <v>12.02</v>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="G88" s="3" t="n">
         <v>0.2166615750083587</v>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H88" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="I86" s="2" t="n">
+      <c r="I88" s="3" t="n">
         <v>-67.71679839697205</v>
       </c>
-      <c r="J86" s="4" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tata Steel Ltd
 </t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="D89" s="3" t="n">
         <v>48.97</v>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="E89" s="3" t="n">
         <v>9.23</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="F89" s="3" t="n">
         <v>38.87</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="G89" s="3" t="n">
         <v>1.638533052351645</v>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="H89" s="3" t="n">
         <v>48.97</v>
       </c>
-      <c r="I87" s="2" t="n">
+      <c r="I89" s="3" t="n">
         <v>-11.95613088816972</v>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Tata Consultancy Services Ltd</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D90" s="3" t="n">
         <v>78.69</v>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="E90" s="3" t="n">
         <v>6.08</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="F90" s="3" t="n">
         <v>29.94</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="G90" s="3" t="n">
         <v>10.93458277277939</v>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="H90" s="3" t="n">
         <v>57.2</v>
       </c>
-      <c r="I88" s="2" t="n">
+      <c r="I90" s="3" t="n">
         <v>23.66808109382366</v>
       </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>Tech Mahindra Ltd</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D91" s="3" t="n">
         <v>57.4</v>
       </c>
-      <c r="E89" s="2" t="n">
+      <c r="E91" s="3" t="n">
         <v>7.43</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="F91" s="3" t="n">
         <v>7.85</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="G91" s="3" t="n">
         <v>0.1674227036387368</v>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="H91" s="3" t="n">
         <v>51.58</v>
       </c>
-      <c r="I89" s="2" t="n">
+      <c r="I91" s="3" t="n">
         <v>-9.790979097909801</v>
       </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Titan Company Ltd
 </t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D92" s="3" t="n">
         <v>10.13</v>
       </c>
-      <c r="E90" s="2" t="n">
+      <c r="E92" s="3" t="n">
         <v>10.51</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="F92" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="G92" s="3" t="n">
         <v>0.0839572651499547</v>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H92" s="3" t="n">
         <v>26.55</v>
       </c>
-      <c r="I90" s="2" t="n">
+      <c r="I92" s="3" t="n">
         <v>-73.3456124194185</v>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>TORNTPHARM</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>Torrent Pharmaceuticals Ltd</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D93" s="3" t="n">
         <v>46.4</v>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E93" s="3" t="n">
         <v>6.43</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="F93" s="3" t="n">
         <v>27.93</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="G93" s="3" t="n">
         <v>0.1660811237632738</v>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="H93" s="3" t="n">
         <v>46.4</v>
       </c>
-      <c r="I91" s="2" t="n">
+      <c r="I93" s="3" t="n">
         <v>-1.402464938376546</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>Trent Ltd</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D94" s="3" t="n">
         <v>8.65</v>
       </c>
-      <c r="E92" s="2" t="n">
+      <c r="E94" s="3" t="n">
         <v>11.82</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="F94" s="3" t="n">
         <v>34.65</v>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="G94" s="3" t="n">
         <v>0.1472024429514394</v>
       </c>
-      <c r="H92" s="2" t="n">
+      <c r="H94" s="3" t="n">
         <v>65.94</v>
       </c>
-      <c r="I92" s="2" t="n">
+      <c r="I94" s="3" t="n">
         <v>-77.23983686357059</v>
       </c>
-      <c r="J92" s="4" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>Discount</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>TVSMOTOR</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>TVS Motor Company Ltd</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D95" s="3" t="n">
         <v>46.1</v>
       </c>
-      <c r="E93" s="2" t="n">
+      <c r="E95" s="3" t="n">
         <v>5.62</v>
       </c>
-      <c r="F93" s="2" t="n">
+      <c r="F95" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="G93" s="2" t="n">
+      <c r="G95" s="3" t="n">
         <v>-0.8454886074536311</v>
       </c>
-      <c r="H93" s="2" t="n">
+      <c r="H95" s="3" t="n">
         <v>46.1</v>
       </c>
-      <c r="I93" s="2" t="n">
+      <c r="I95" s="3" t="n">
         <v>21.29982896987237</v>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>